--- a/_static/global/profiles.xlsx
+++ b/_static/global/profiles.xlsx
@@ -820,7 +820,11 @@
           <t>more than $4000</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>Not religious</t>
@@ -1018,7 +1022,11 @@
           <t>less than $1000</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>Not religious</t>
@@ -1620,7 +1628,11 @@
           <t>$1000-$1999</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>Orthodox</t>
@@ -2745,7 +2757,11 @@
           <t>less than $1000</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>Protestant</t>
@@ -3355,7 +3371,11 @@
           <t>less than $1000</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr">
         <is>
           <t>Other</t>
@@ -5502,7 +5522,11 @@
           <t>$3000-$3999</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T50" t="inlineStr">
         <is>
           <t>Other</t>
@@ -6112,7 +6136,11 @@
           <t>$2000-$2999</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T56" t="inlineStr">
         <is>
           <t>Catholic</t>
@@ -7744,7 +7772,11 @@
           <t>less than $1000</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T72" t="inlineStr">
         <is>
           <t>Protestant</t>
@@ -13880,7 +13912,11 @@
           <t>less than $1000</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T132" t="inlineStr">
         <is>
           <t>Not religious</t>
@@ -14684,7 +14720,11 @@
           <t>more than $4000</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr"/>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T140" t="inlineStr">
         <is>
           <t>Protestant</t>
@@ -15805,7 +15845,11 @@
           <t>$2000-$2999</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T151" t="inlineStr">
         <is>
           <t>Other</t>
@@ -16007,7 +16051,11 @@
           <t>$2000-$2999</t>
         </is>
       </c>
-      <c r="S153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T153" t="inlineStr">
         <is>
           <t>Catholic</t>
@@ -18966,7 +19014,11 @@
           <t>$3000-$3999</t>
         </is>
       </c>
-      <c r="S182" t="inlineStr"/>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T182" t="inlineStr">
         <is>
           <t>Protestant</t>
@@ -20915,7 +20967,11 @@
           <t>$1000-$1999</t>
         </is>
       </c>
-      <c r="S201" t="inlineStr"/>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T201" t="inlineStr">
         <is>
           <t>Catholic</t>
@@ -21117,7 +21173,11 @@
           <t>more than $4000</t>
         </is>
       </c>
-      <c r="S203" t="inlineStr"/>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T203" t="inlineStr">
         <is>
           <t>Catholic</t>
@@ -21830,7 +21890,11 @@
           <t>$1000-$1999</t>
         </is>
       </c>
-      <c r="S210" t="inlineStr"/>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T210" t="inlineStr">
         <is>
           <t>Protestant</t>
@@ -21929,7 +21993,11 @@
           <t>$1000-$1999</t>
         </is>
       </c>
-      <c r="S211" t="inlineStr"/>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T211" t="inlineStr">
         <is>
           <t>Other</t>
@@ -24072,7 +24140,11 @@
           <t>$2000-$2999</t>
         </is>
       </c>
-      <c r="S232" t="inlineStr"/>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T232" t="inlineStr">
         <is>
           <t>Not religious</t>
@@ -25086,7 +25158,11 @@
           <t>$3000-$3999</t>
         </is>
       </c>
-      <c r="S242" t="inlineStr"/>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="T242" t="inlineStr">
         <is>
           <t>Catholic</t>

--- a/_static/global/profiles.xlsx
+++ b/_static/global/profiles.xlsx
@@ -598,7 +598,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
         <v>3</v>
@@ -800,7 +804,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>3</v>
@@ -899,7 +907,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>3</v>
@@ -998,7 +1010,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>biology</t>
@@ -1101,7 +1117,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
         <v>4</v>
@@ -1505,7 +1525,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
         <v>3</v>
@@ -2016,7 +2040,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>5</v>
@@ -2939,7 +2967,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
         <v>5</v>
@@ -3862,7 +3894,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
         <v>5</v>
@@ -4064,7 +4100,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>Social Work</t>
@@ -4579,7 +4619,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
         <v>5</v>
@@ -4884,7 +4928,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
         <v>6</v>
@@ -5807,7 +5855,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
         <v>4</v>
@@ -7348,7 +7400,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>6</v>
@@ -7447,7 +7503,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
         <v>5</v>
@@ -7752,7 +7812,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>5</v>
@@ -7847,7 +7911,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
         <v>3</v>
@@ -9182,7 +9250,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
         <v>4</v>
@@ -9899,7 +9971,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="n">
         <v>5</v>
@@ -10509,7 +10585,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
         <v>5</v>
@@ -11226,7 +11306,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
         <v>5</v>
@@ -12046,7 +12130,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="n">
         <v>3</v>
@@ -12351,7 +12439,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr">
         <is>
           <t>finance</t>
@@ -12969,7 +13061,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="n">
         <v>5</v>
@@ -13171,7 +13267,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="n">
         <v>4</v>
@@ -13991,7 +14091,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="n">
         <v>2</v>
@@ -14193,7 +14297,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="n">
         <v>3</v>
@@ -14292,7 +14400,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="n">
         <v>4</v>
@@ -14391,7 +14503,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="n">
         <v>5</v>
@@ -15005,7 +15121,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="n">
         <v>4</v>
@@ -15619,7 +15739,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="n">
         <v>3</v>
@@ -16233,7 +16357,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr">
         <is>
           <t>Space Studies</t>
@@ -16439,7 +16567,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr">
         <is>
           <t xml:space="preserve">history </t>
@@ -16851,7 +16983,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="n">
         <v>2</v>
@@ -17259,7 +17395,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="n">
         <v>3</v>
@@ -17461,7 +17601,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="n">
         <v>3</v>
@@ -17869,7 +18013,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="n">
         <v>4</v>
@@ -17968,7 +18116,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N172" t="inlineStr">
         <is>
           <t>Computer Science</t>
@@ -18071,7 +18223,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N173" t="inlineStr">
         <is>
           <t>Art and design</t>
@@ -18277,7 +18433,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="n">
         <v>2</v>
@@ -18788,7 +18948,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N180" t="inlineStr">
         <is>
           <t>Healthcare</t>
@@ -18994,7 +19158,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="n">
         <v>6</v>
@@ -19093,7 +19261,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N183" t="inlineStr">
         <is>
           <t>Information Technology</t>
@@ -20947,7 +21119,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="n">
         <v>3</v>
@@ -21252,7 +21428,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N204" t="inlineStr">
         <is>
           <t>Mathematics and computer science</t>
@@ -21458,7 +21638,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N206" t="inlineStr">
         <is>
           <t>Information Technology</t>
@@ -21870,7 +22054,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="n">
         <v>5</v>
@@ -22896,7 +23084,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N220" t="inlineStr">
         <is>
           <t>Masters in Mathematic and Statistics and also a part time employee</t>
@@ -22999,7 +23191,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="n">
         <v>5</v>
@@ -23098,7 +23294,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N222" t="inlineStr">
         <is>
           <t>Nursing</t>
@@ -23613,7 +23813,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="n">
         <v>6</v>
@@ -23918,7 +24122,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="n">
         <v>2</v>
@@ -24017,7 +24225,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="n">
         <v>2</v>
@@ -24219,7 +24431,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="n">
         <v>3</v>
@@ -24318,7 +24534,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="n">
         <v>2</v>
@@ -25134,7 +25354,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N242" t="inlineStr">
         <is>
           <t>Data science</t>
@@ -25443,7 +25667,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N245" t="inlineStr">
         <is>
           <t>Information Technology</t>
@@ -26576,7 +26804,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="n">
         <v>0</v>
@@ -26881,7 +27113,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="n">
         <v>5</v>
@@ -28113,7 +28349,11 @@
           <t>male</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="n">
         <v>3</v>
@@ -28212,7 +28452,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="n">
         <v>2</v>
